--- a/template.xlsx
+++ b/template.xlsx
@@ -5,18 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Scripts\lemure_viewer_local_debug\lab_viewer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.baidenko\Desktop\мусор\Лаба\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64348C4D-C207-46CC-A58F-05C8958E3725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74ABFDD-1E97-4462-BB7B-22C139C265DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="2475" windowWidth="21600" windowHeight="11295" xr2:uid="{567E23D1-9027-490D-A6E6-D7650005BE01}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{567E23D1-9027-490D-A6E6-D7650005BE01}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
   <si>
     <t>Время испытания, мин</t>
   </si>
@@ -125,9 +124,6 @@
   </si>
   <si>
     <t>R290</t>
-  </si>
-  <si>
-    <t>R600a</t>
   </si>
 </sst>
 </file>
@@ -138,7 +134,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="[h]:mm:ss;@"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,23 +207,6 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -481,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -633,8 +612,6 @@
     <xf numFmtId="164" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -953,13 +930,12 @@
   <dimension ref="B1:BC4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:55" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="51" t="s">
+    <row r="1" spans="2:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="52"/>
     </row>
-    <row r="2" spans="2:55" ht="150" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:55" ht="148.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1324,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="Y4" s="37" t="e">
-        <f t="shared" ref="Y4" si="2">AVERAGE(Z4:BE4)</f>
+        <f>AVERAGE(Z4:BE4)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Z4" s="38"/>
@@ -1360,37 +1336,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F2FD8596-8BE8-4113-8455-D1BEFDF8E7A2}">
-          <x14:formula1>
-            <xm:f>Лист2!$A$1:$A$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>B1</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7509EAE0-6145-4BE5-BC0F-D07042B44FBA}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/template.xlsx
+++ b/template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.baidenko\Desktop\мусор\Лаба\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.baidenko\Downloads\JSQ-Laboratory\JSQ_Viewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74ABFDD-1E97-4462-BB7B-22C139C265DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FF3F08-22B5-4423-8C88-37D5CC9EB6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{567E23D1-9027-490D-A6E6-D7650005BE01}"/>
   </bookViews>
@@ -1284,12 +1284,20 @@
       <c r="S4" s="49"/>
       <c r="T4" s="49"/>
       <c r="U4" s="34">
-        <f>IF($B$1="R290",0.00005*D4^5-0.0037*D4^4+0.1052*D4^3-1.5247*D4^2+14.856*D4-38.823,IF($B$1="R600a",0.001*D4^5-0.042*D4^4+0.6637*D4^3-5.0642*D4^2+24.812*D4-13.145,0))</f>
-        <v>-38.823</v>
+        <f>IF($B$1="R290",
+IF(OR(D4&lt;-0.48,D4&gt;41.359),"ВНЕ ДИАПАЗОНА",0.01973273385328*LN(D4+1)^4+0.2987622586022*LN(D4+1)^3+2.452863797722*LN(D4+1)^2+22.63007347287*LN(D4+1)-42.19015299063),
+IF($B$1="R600a",
+IF(OR(D4&lt;-0.79,D4&gt;32.143),"ВНЕ ДИАПАЗОНА",0.043751593072*LN(D4+1)^4+0.261943878832*LN(D4+1)^3+2.781284406656*LN(D4+1)^2+25.461831417726*LN(D4+1)-12.189730454141),
+0))</f>
+        <v>-42.190152990629997</v>
       </c>
       <c r="V4" s="50">
-        <f>IF($B$1="R290",0.00005*E4^5-0.0037*E4^4+0.1052*E4^3-1.5247*E4^2+14.856*E4-38.823,IF($B$1="R600a",0.001*E4^5-0.042*E4^4+0.6637*E4^3-5.0642*E4^2+24.812*E4-13.145,0))</f>
-        <v>-38.823</v>
+        <f>IF($B$1="R290",
+IF(OR(E4&lt;-0.48,E4&gt;41.359),"ВНЕ ДИАПАЗОНА",0.01973273385328*LN(E4+1)^4+0.2987622586022*LN(E4+1)^3+2.452863797722*LN(E4+1)^2+22.63007347287*LN(E4+1)-42.19015299063),
+IF($B$1="R600a",
+IF(OR(E4&lt;-0.79,E4&gt;32.143),"ВНЕ ДИАПАЗОНА",0.043751593072*LN(E4+1)^4+0.261943878832*LN(E4+1)^3+2.781284406656*LN(E4+1)^2+25.461831417726*LN(E4+1)-12.189730454141),
+0))</f>
+        <v>-42.190152990629997</v>
       </c>
       <c r="W4" s="35">
         <f t="shared" ref="W4" si="0">MIN(Z4:BM4)</f>
